--- a/sampleprojects/CorporateTax/excel/states/WA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/WA_corp.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t>DT: Determine WA Filing Requirement</t>
   </si>
@@ -101,7 +101,7 @@
     <t>No nexus - no filing required; No Washington nexus - no B&amp;O tax filing requirement</t>
   </si>
   <si>
-    <t>set result.wa_bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington nexus - no B&amp;O tax filing requirement. Any estimated payments would be refunded." to job.audit_trail;</t>
+    <t>set wa_result.bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington nexus - no B&amp;O tax filing requirement. Any estimated payments would be refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate WA Gross Receipts</t>
@@ -128,19 +128,19 @@
     <t>Calculate WA gross receipts using apportionment; Calculate WA-sourced gross receipts using apportionment percentage</t>
   </si>
   <si>
-    <t>set result.wa_gross_receipts = revenue.total_revenue * apportionment.apportionment_percentage; add "Washington gross receipts calculation for B&amp;O tax using market-based sourcing. Reference: RCW 82.04.460" to job.audit_trail;</t>
+    <t>set wa_result.gross_receipts = revenue.total_revenue * apportionment.apportionment_percentage; add "Washington gross receipts calculation for B&amp;O tax using market-based sourcing. Reference: RCW 82.04.460" to job.audit_trail;</t>
   </si>
   <si>
     <t>No apportionment - assume 100% WA; No apportionment calculated - treating all receipts as Washington-sourced</t>
   </si>
   <si>
-    <t>set result.wa_gross_receipts = revenue.total_revenue; add "No apportionment percentage - treating all receipts as Washington-sourced." to job.audit_trail;</t>
+    <t>set wa_result.gross_receipts = revenue.total_revenue; add "No apportionment percentage - treating all receipts as Washington-sourced." to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no WA gross receipts; No Washington nexus - no gross receipts attributed to Washington</t>
   </si>
   <si>
-    <t>set result.wa_gross_receipts = 0.0; add "No Washington nexus - no gross receipts attributed to Washington." to job.audit_trail;</t>
+    <t>set wa_result.gross_receipts = 0.0; add "No Washington nexus - no gross receipts attributed to Washington." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Determine WA Business Classification</t>
@@ -155,364 +155,340 @@
     <t>Business classification code</t>
   </si>
   <si>
-    <t>result.wa_business_classification</t>
-  </si>
-  <si>
-    <t>retailing</t>
-  </si>
-  <si>
-    <t>wholesaling</t>
-  </si>
-  <si>
-    <t>manufacturing</t>
-  </si>
-  <si>
-    <t>financial</t>
-  </si>
-  <si>
-    <t>professional</t>
+    <t>wa_result.business_classification</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Retailing B&amp;O rate: 0.471%; Set retailing B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.retailing_rate; add "Washington B&amp;O tax - Retailing classification: 0.471%. Retailing includes sales of tangible personal property to consumers for consumption or use (not for resale). References: RCW 82.04.250 (Retailing), RCW 82.04.470 (Retailing B&amp;O Tax Rate)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>Wholesaling B&amp;O rate: 0.484%; Set wholesaling B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.wholesaling_rate; add "Washington B&amp;O tax - Wholesaling classification: 0.484%. Wholesaling includes sales of tangible personal property to persons for purpose of resale. References: RCW 82.04.060 (Wholesaling), RCW 82.04.270 (Wholesaling B&amp;O Tax)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>Manufacturing B&amp;O rate: 0.484%; Set manufacturing B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.manufacturing_rate; add "Washington B&amp;O tax - Manufacturing classification: 0.484%. Manufacturing includes production of articles for sale from raw materials, including processing, fabricating, assembling, extracting. Note: Certain manufacturers may qualify for preferential rates or exemptions. References: RCW 82.04.240 (Manufacturing), RCW 82.04.440 (Manufacturing B&amp;O Tax)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>Financial Business B&amp;O rate: 1.5%; Set financial business B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.financial_rate; add "Washington B&amp;O tax - Financial Business classification: 1.5% (highest rate). Financial business includes banks, savings and loan associations, credit unions, finance companies, insurance companies, and similar institutions. Reference: RCW 82.04.290 (Financial Business)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>Professional Services B&amp;O rate: 0.484%; Set professional services B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.professional_rate; add "Washington B&amp;O tax - Professional Services classification: 0.484%. Professional services include legal, accounting, engineering, consulting, and other professional activities. Reference: RCW 82.04.290 (Service and Other Activities)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>Service and Other Activities B&amp;O rate: 0.484%; Set service and other activities B&amp;O tax rate</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax_rate = wa_result.service_rate; add "Washington B&amp;O tax - Service and Other Activities classification: 0.484%. This is the catch-all classification for business activities not specifically classified elsewhere. Reference: RCW 82.04.290 (Service and Other Activities)" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>DT: Calculate WA Small Business Credit</t>
+  </si>
+  <si>
+    <t>COMMENTS: Calculates the Washington small business B&amp;O tax credit. Small Business B&amp;O Credit: Available for businesses with gross revenue under $250,000, credit amount varies based on total revenue and phases out as revenue increases, reduces B&amp;O tax liability (can reduce to zero but not create refund). Maximum credit approximately $100-120 per month ($1,200-1,440 annually). References: RCW 82.04.4451 (Small Business B&amp;O Credit), WAC 458-20-104 (Small Business Tax Relief).</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51060</t>
+  </si>
+  <si>
+    <t>Total revenue below $250K small business threshold; revenue.total_revenue &lt; result.wa_small_business_credit_threshold</t>
+  </si>
+  <si>
+    <t>revenue.total_revenue &lt; wa_result.small_business_credit_threshold</t>
+  </si>
+  <si>
+    <t>Has Washington gross receipts subject to B&amp;O tax</t>
+  </si>
+  <si>
+    <t>wa_result.gross_receipts &gt; 0</t>
+  </si>
+  <si>
+    <t>Qualifies for small business B&amp;O credit; Calculate small business credit (phases out as revenue approaches $250K)</t>
+  </si>
+  <si>
+    <t>set wa_result.qualifies_for_small_business_credit = true; set wa_result.small_business_credit = 1440.0 * (1.0 - revenue.total_revenue / wa_result.small_business_credit_threshold); add "Washington Small Business B&amp;O Tax Credit applied. Revenue under $250K. Reference: RCW 82.04.4451" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>No credit - revenue exceeds threshold; No small business credit - gross revenue exceeds $250,000 threshold</t>
+  </si>
+  <si>
+    <t>set wa_result.qualifies_for_small_business_credit = false; set wa_result.small_business_credit = 0.0; add "No small business credit - gross revenue exceeds $250,000 threshold." to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>No credit - no WA gross receipts; No small business credit - no Washington gross receipts to apply credit against</t>
+  </si>
+  <si>
+    <t>set wa_result.qualifies_for_small_business_credit = false; set wa_result.small_business_credit = 0.0; add "No small business credit - no Washington gross receipts." to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>DT: Calculate WA BO Tax</t>
+  </si>
+  <si>
+    <t>COMMENTS: Calculates final Washington Business and Occupation (B&amp;O) tax liability. IMPORTANT: Washington has NO corporate income tax. The B&amp;O tax is a gross receipts tax, NOT an income tax. Process: 1) Calculate WA-sourced gross receipts (table 51020), 2) Determine business classification rate (table 51040), 3) Calculate B&amp;O tax = gross receipts × B&amp;O rate, 4) Apply small business credit (table 51060), 5) Apply other credits (high tech, aerospace), 6) Calculate refund or amount owed. Key Differences from Income Tax: Based on GROSS RECEIPTS (revenue) not net income, no deductions for expenses/COGS/payroll, much lower rates (under 1.5%) but applies to gross revenue, must be paid even if business operates at a loss. References: RCW 82.04 (Business and Occupation Tax), WAC 458-20-104 (Small Business Tax Relief), Form ETA (Combined Excise Tax Return).</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51080</t>
+  </si>
+  <si>
+    <t>Must have nexus to owe B&amp;O tax; apportionment.has_economic_nexus == true OR apportionment.has_physical_presence == true</t>
+  </si>
+  <si>
+    <t>Has positive Washington gross receipts</t>
+  </si>
+  <si>
+    <t>Calculate B&amp;O tax with all credits; Calculate Washington B&amp;O tax on gross receipts and apply all credits</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax = wa_result.gross_receipts * wa_result.bo_tax_rate; set wa_result.bo_tax = the maximum of (wa_result.bo_tax - wa_result.small_business_credit) and (0.0); set wa_result.bo_tax = the maximum of (wa_result.bo_tax - wa_result.high_tech_credit) and (0.0); set wa_result.bo_tax = the maximum of (wa_result.bo_tax - wa_result.aerospace_credit) and (0.0); set wa_result.bo_tax = the maximum of (wa_result.bo_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = wa_result.bo_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "Washington B&amp;O Tax calculated. Gross receipts tax, NOT income tax. Reference: RCW 82.04" to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>No nexus - no B&amp;O tax; No Washington nexus - no B&amp;O tax liability</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington nexus - no B&amp;O tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>No WA gross receipts - no B&amp;O tax; No Washington gross receipts - no B&amp;O tax liability</t>
+  </si>
+  <si>
+    <t>set wa_result.bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington gross receipts - no B&amp;O tax liability. Filing may still be required to report no tax due." to job.audit_trail;</t>
+  </si>
+  <si>
+    <t>DT: Calculate WA Income Adjustments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 55150</t>
+  </si>
+  <si>
+    <t>wrapper: dispatch arrives here for WA</t>
+  </si>
+  <si>
+    <t>apportionment.state_code == "WA"</t>
+  </si>
+  <si>
+    <t>performs the state's real computation</t>
+  </si>
+  <si>
+    <t>perform Determine_WA_Business_Classification</t>
+  </si>
+  <si>
+    <t>perform Calculate_WA_Gross_Receipts</t>
+  </si>
+  <si>
+    <t>DT: Calculate WA State Tax</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 55160</t>
+  </si>
+  <si>
+    <t>perform Calculate_WA_BO_Tax</t>
+  </si>
+  <si>
+    <t>perform Calculate_WA_Small_Business_Credit</t>
+  </si>
+  <si>
+    <t>EDD: EDD</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SubType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>wa_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
+  </si>
+  <si>
+    <t>apportionment_formula</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>single_sales</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Washington uses single-sales factor for sourcing receipts to Washington</t>
+  </si>
+  <si>
+    <t>economic_nexus_threshold</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>100000.0</t>
+  </si>
+  <si>
+    <t>Washington economic nexus: $100,000 in Washington receipts (follows Wayfair standard)</t>
+  </si>
+  <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Washington has NO corporate income tax (B&amp;O tax is calculated separately)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Washington economic nexus: 200 or more separate transactions</t>
+  </si>
+  <si>
+    <t>wa_result</t>
+  </si>
+  <si>
+    <t>(16 attributes)</t>
+  </si>
+  <si>
+    <t>aerospace_credit</t>
+  </si>
+  <si>
+    <t>Washington aerospace industry B&amp;O tax credit</t>
+  </si>
+  <si>
+    <t>bo_tax</t>
+  </si>
+  <si>
+    <t>Washington B&amp;O tax liability (NOT an income tax - based on gross receipts)</t>
+  </si>
+  <si>
+    <t>bo_tax_rate</t>
+  </si>
+  <si>
+    <t>0.00484</t>
+  </si>
+  <si>
+    <t>WA B&amp;O tax rate based on business classification (0.484% default for service/other)</t>
+  </si>
+  <si>
+    <t>business_classification</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
-    <t>Retailing B&amp;O rate: 0.471%; Set retailing B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_retailing_rate; add "Washington B&amp;O tax - Retailing classification: 0.471%. Retailing includes sales of tangible personal property to consumers for consumption or use (not for resale). References: RCW 82.04.250 (Retailing), RCW 82.04.470 (Retailing B&amp;O Tax Rate)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>Wholesaling B&amp;O rate: 0.484%; Set wholesaling B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_wholesaling_rate; add "Washington B&amp;O tax - Wholesaling classification: 0.484%. Wholesaling includes sales of tangible personal property to persons for purpose of resale. References: RCW 82.04.060 (Wholesaling), RCW 82.04.270 (Wholesaling B&amp;O Tax)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>Manufacturing B&amp;O rate: 0.484%; Set manufacturing B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_manufacturing_rate; add "Washington B&amp;O tax - Manufacturing classification: 0.484%. Manufacturing includes production of articles for sale from raw materials, including processing, fabricating, assembling, extracting. Note: Certain manufacturers may qualify for preferential rates or exemptions. References: RCW 82.04.240 (Manufacturing), RCW 82.04.440 (Manufacturing B&amp;O Tax)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>Financial Business B&amp;O rate: 1.5%; Set financial business B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_financial_rate; add "Washington B&amp;O tax - Financial Business classification: 1.5% (highest rate). Financial business includes banks, savings and loan associations, credit unions, finance companies, insurance companies, and similar institutions. Reference: RCW 82.04.290 (Financial Business)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>Professional Services B&amp;O rate: 0.484%; Set professional services B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_professional_rate; add "Washington B&amp;O tax - Professional Services classification: 0.484%. Professional services include legal, accounting, engineering, consulting, and other professional activities. Reference: RCW 82.04.290 (Service and Other Activities)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>Service and Other Activities B&amp;O rate: 0.484%; Set service and other activities B&amp;O tax rate</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax_rate = result.wa_service_rate; add "Washington B&amp;O tax - Service and Other Activities classification: 0.484%. This is the catch-all classification for business activities not specifically classified elsewhere. Reference: RCW 82.04.290 (Service and Other Activities)" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>DT: Calculate WA Small Business Credit</t>
-  </si>
-  <si>
-    <t>COMMENTS: Calculates the Washington small business B&amp;O tax credit. Small Business B&amp;O Credit: Available for businesses with gross revenue under $250,000, credit amount varies based on total revenue and phases out as revenue increases, reduces B&amp;O tax liability (can reduce to zero but not create refund). Maximum credit approximately $100-120 per month ($1,200-1,440 annually). References: RCW 82.04.4451 (Small Business B&amp;O Credit), WAC 458-20-104 (Small Business Tax Relief).</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 51060</t>
-  </si>
-  <si>
-    <t>Total revenue below $250K small business threshold; revenue.total_revenue &lt; result.wa_small_business_credit_threshold</t>
-  </si>
-  <si>
-    <t>revenue.total_revenue &lt; result.wa_small_business_credit_threshold</t>
-  </si>
-  <si>
-    <t>Has Washington gross receipts subject to B&amp;O tax</t>
-  </si>
-  <si>
-    <t>result.wa_gross_receipts &gt; 0</t>
-  </si>
-  <si>
-    <t>Qualifies for small business B&amp;O credit; Calculate small business credit (phases out as revenue approaches $250K)</t>
-  </si>
-  <si>
-    <t>set result.wa_qualifies_for_small_business_credit = true; set result.wa_small_business_credit = 1440.0 * (1.0 - revenue.total_revenue / result.wa_small_business_credit_threshold); add "Washington Small Business B&amp;O Tax Credit applied. Revenue under $250K. Reference: RCW 82.04.4451" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>No credit - revenue exceeds threshold; No small business credit - gross revenue exceeds $250,000 threshold</t>
-  </si>
-  <si>
-    <t>set result.wa_qualifies_for_small_business_credit = false; set result.wa_small_business_credit = 0.0; add "No small business credit - gross revenue exceeds $250,000 threshold." to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>No credit - no WA gross receipts; No small business credit - no Washington gross receipts to apply credit against</t>
-  </si>
-  <si>
-    <t>set result.wa_qualifies_for_small_business_credit = false; set result.wa_small_business_credit = 0.0; add "No small business credit - no Washington gross receipts." to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>DT: Calculate WA BO Tax</t>
-  </si>
-  <si>
-    <t>COMMENTS: Calculates final Washington Business and Occupation (B&amp;O) tax liability. IMPORTANT: Washington has NO corporate income tax. The B&amp;O tax is a gross receipts tax, NOT an income tax. Process: 1) Calculate WA-sourced gross receipts (table 51020), 2) Determine business classification rate (table 51040), 3) Calculate B&amp;O tax = gross receipts × B&amp;O rate, 4) Apply small business credit (table 51060), 5) Apply other credits (high tech, aerospace), 6) Calculate refund or amount owed. Key Differences from Income Tax: Based on GROSS RECEIPTS (revenue) not net income, no deductions for expenses/COGS/payroll, much lower rates (under 1.5%) but applies to gross revenue, must be paid even if business operates at a loss. References: RCW 82.04 (Business and Occupation Tax), WAC 458-20-104 (Small Business Tax Relief), Form ETA (Combined Excise Tax Return).</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 51080</t>
-  </si>
-  <si>
-    <t>Must have nexus to owe B&amp;O tax; apportionment.has_economic_nexus == true OR apportionment.has_physical_presence == true</t>
-  </si>
-  <si>
-    <t>Has positive Washington gross receipts</t>
-  </si>
-  <si>
-    <t>Calculate B&amp;O tax with all credits; Calculate Washington B&amp;O tax on gross receipts and apply all credits</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax = result.wa_gross_receipts * result.wa_bo_tax_rate; set result.wa_bo_tax = the maximum of (result.wa_bo_tax - result.wa_small_business_credit) and (0.0); set result.wa_bo_tax = the maximum of (result.wa_bo_tax - result.wa_high_tech_credit) and (0.0); set result.wa_bo_tax = the maximum of (result.wa_bo_tax - result.wa_aerospace_credit) and (0.0); set result.wa_bo_tax = the maximum of (result.wa_bo_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = result.wa_bo_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "Washington B&amp;O Tax calculated. Gross receipts tax, NOT income tax. Reference: RCW 82.04" to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>No nexus - no B&amp;O tax; No Washington nexus - no B&amp;O tax liability</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington nexus - no B&amp;O tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>No WA gross receipts - no B&amp;O tax; No Washington gross receipts - no B&amp;O tax liability</t>
-  </si>
-  <si>
-    <t>set result.wa_bo_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Washington gross receipts - no B&amp;O tax liability. Filing may still be required to report no tax due." to job.audit_trail;</t>
-  </si>
-  <si>
-    <t>DT: Calculate WA Income Adjustments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMENTS: </t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 55150</t>
-  </si>
-  <si>
-    <t>wrapper: dispatch arrives here for WA</t>
-  </si>
-  <si>
-    <t>apportionment.state_code == "WA"</t>
-  </si>
-  <si>
-    <t>performs the state's real computation</t>
-  </si>
-  <si>
-    <t>perform Determine_WA_Business_Classification</t>
-  </si>
-  <si>
-    <t>perform Calculate_WA_Gross_Receipts</t>
-  </si>
-  <si>
-    <t>DT: Calculate WA State Tax</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 55160</t>
-  </si>
-  <si>
-    <t>perform Calculate_WA_BO_Tax</t>
-  </si>
-  <si>
-    <t>perform Calculate_WA_Small_Business_Credit</t>
-  </si>
-  <si>
-    <t>EDD: EDD</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>SubType</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Access</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Collect</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Q Type</t>
-  </si>
-  <si>
-    <t>Options</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
-  </si>
-  <si>
-    <t>apportionment_formula</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>single_sales</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>rw</t>
-  </si>
-  <si>
-    <t>Washington uses single-sales factor for sourcing receipts to Washington</t>
-  </si>
-  <si>
-    <t>economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>100000.0</t>
-  </si>
-  <si>
-    <t>Washington economic nexus: $100,000 in Washington receipts (follows Wayfair standard)</t>
-  </si>
-  <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>Not applicable - Washington has no income tax</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>Washington state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>Washington B&amp;O tax credits (small business credit, high tech, aerospace, etc.)</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>Washington has NO corporate income tax (B&amp;O tax is calculated separately)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Washington economic nexus: 200 or more separate transactions</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(16 attributes)</t>
-  </si>
-  <si>
-    <t>wa_aerospace_credit</t>
-  </si>
-  <si>
-    <t>Washington aerospace industry B&amp;O tax credit</t>
-  </si>
-  <si>
-    <t>wa_bo_tax</t>
-  </si>
-  <si>
-    <t>Washington B&amp;O tax liability (NOT an income tax - based on gross receipts)</t>
-  </si>
-  <si>
-    <t>wa_bo_tax_rate</t>
-  </si>
-  <si>
-    <t>0.00484</t>
-  </si>
-  <si>
-    <t>WA B&amp;O tax rate based on business classification (0.484% default for service/other)</t>
-  </si>
-  <si>
-    <t>wa_business_classification</t>
-  </si>
-  <si>
     <t>WA business classification: service, retailing, wholesaling, manufacturing, professional, financial</t>
   </si>
   <si>
-    <t>wa_financial_rate</t>
+    <t>financial_rate</t>
   </si>
   <si>
     <t>0.015</t>
   </si>
   <si>
-    <t>r</t>
-  </si>
-  <si>
     <t>Financial Business B&amp;O rate: 1.5%</t>
   </si>
   <si>
-    <t>wa_gross_receipts</t>
+    <t>gross_receipts</t>
   </si>
   <si>
     <t>Washington-sourced gross receipts for B&amp;O tax (all revenue from WA activities)</t>
   </si>
   <si>
-    <t>wa_high_tech_credit</t>
+    <t>high_tech_credit</t>
   </si>
   <si>
     <t>Washington high-tech B&amp;O tax credit</t>
   </si>
   <si>
-    <t>wa_manufacturing_rate</t>
+    <t>manufacturing_rate</t>
   </si>
   <si>
     <t>Manufacturing B&amp;O rate: 0.484%</t>
   </si>
   <si>
-    <t>wa_professional_rate</t>
+    <t>professional_rate</t>
   </si>
   <si>
     <t>Professional Services B&amp;O rate: 0.484%</t>
   </si>
   <si>
-    <t>wa_qualifies_for_manufacturing_exemption</t>
+    <t>qualifies_for_manufacturing_exemption</t>
   </si>
   <si>
     <t>boolean</t>
@@ -524,13 +500,13 @@
     <t>Qualifies for B&amp;O manufacturing tax exemptions or preferential rates</t>
   </si>
   <si>
-    <t>wa_qualifies_for_small_business_credit</t>
+    <t>qualifies_for_small_business_credit</t>
   </si>
   <si>
     <t>Qualifies for Washington small business B&amp;O credit</t>
   </si>
   <si>
-    <t>wa_retailing_rate</t>
+    <t>retailing_rate</t>
   </si>
   <si>
     <t>0.00471</t>
@@ -539,19 +515,19 @@
     <t>Retailing B&amp;O rate: 0.471%</t>
   </si>
   <si>
-    <t>wa_service_rate</t>
+    <t>service_rate</t>
   </si>
   <si>
     <t>Service and Other Activities B&amp;O rate: 0.484%</t>
   </si>
   <si>
-    <t>wa_small_business_credit</t>
+    <t>small_business_credit</t>
   </si>
   <si>
     <t>Washington small business B&amp;O credit amount</t>
   </si>
   <si>
-    <t>wa_small_business_credit_threshold</t>
+    <t>small_business_credit_threshold</t>
   </si>
   <si>
     <t>250000.0</t>
@@ -560,7 +536,7 @@
     <t>Small business B&amp;O credit available for businesses with gross revenue under $250K</t>
   </si>
   <si>
-    <t>wa_wholesaling_rate</t>
+    <t>wholesaling_rate</t>
   </si>
   <si>
     <t>Wholesaling B&amp;O rate: 0.484%</t>
@@ -5135,14 +5111,14 @@
       <c r="B7" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>116</v>
+      <c r="C7" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>118</v>
@@ -5151,7 +5127,7 @@
         <v>119</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -5170,194 +5146,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>119</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>119</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="H12" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>122</v>
@@ -5366,16 +5342,16 @@
         <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>118</v>
+        <v>145</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>14</v>
@@ -5398,7 +5374,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>122</v>
@@ -5416,7 +5392,7 @@
         <v>119</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>14</v>
@@ -5439,7 +5415,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>122</v>
@@ -5448,16 +5424,16 @@
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
+        <v>126</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>119</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>14</v>
@@ -5480,25 +5456,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>116</v>
+        <v>151</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>118</v>
+        <v>139</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>14</v>
@@ -5521,7 +5497,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>122</v>
@@ -5530,13 +5506,13 @@
         <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>154</v>
@@ -5564,14 +5540,14 @@
       <c r="B18" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>122</v>
+      <c r="C18" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>14</v>
@@ -5580,7 +5556,7 @@
         <v>119</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>14</v>
@@ -5603,25 +5579,25 @@
         <v>14</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>118</v>
+      <c r="F19" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>119</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>14</v>
@@ -5644,7 +5620,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>122</v>
@@ -5653,16 +5629,16 @@
         <v>14</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>14</v>
@@ -5685,7 +5661,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>122</v>
@@ -5694,16 +5670,16 @@
         <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>14</v>
@@ -5726,16 +5702,16 @@
         <v>14</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>14</v>
@@ -5744,7 +5720,7 @@
         <v>119</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>14</v>
@@ -5767,25 +5743,25 @@
         <v>14</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>164</v>
+        <v>168</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>14</v>
@@ -5808,7 +5784,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>122</v>
@@ -5817,16 +5793,16 @@
         <v>14</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>14</v>
@@ -5841,170 +5817,6 @@
         <v>14</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M28" s="8" t="s">
         <v>14</v>
       </c>
     </row>
